--- a/Desktop Files - Mix/02. Data - EclipseApps/01. Live Project/08. CRE.xlsx
+++ b/Desktop Files - Mix/02. Data - EclipseApps/01. Live Project/08. CRE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Data\01. Live Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05. Daily (21-Mar-26) - 6GB\VSCode\Desktop Files - Mix\02. Data - EclipseApps\01. Live Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768A8085-70CD-458C-84A0-B4C489658C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4184C32C-8884-4BBE-95A1-21BA3DB33D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -946,18 +946,9 @@
       <c r="AL2" t="s">
         <v>48</v>
       </c>
-      <c r="AM2">
-        <v>20250415161255.5</v>
-      </c>
       <c r="AN2" t="s">
         <v>48</v>
       </c>
-      <c r="AO2">
-        <v>20250415161255.5</v>
-      </c>
-      <c r="AP2">
-        <v>20250415161255.5</v>
-      </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1020,18 +1011,9 @@
       <c r="AL3" t="s">
         <v>52</v>
       </c>
-      <c r="AM3">
-        <v>20250415165842.898</v>
-      </c>
       <c r="AN3" t="s">
         <v>52</v>
       </c>
-      <c r="AO3">
-        <v>20250415165842.898</v>
-      </c>
-      <c r="AP3">
-        <v>20250415165842.898</v>
-      </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1094,18 +1076,9 @@
       <c r="AL4" t="s">
         <v>56</v>
       </c>
-      <c r="AM4">
-        <v>20250416093649</v>
-      </c>
       <c r="AN4" t="s">
         <v>56</v>
       </c>
-      <c r="AO4">
-        <v>20250416093649</v>
-      </c>
-      <c r="AP4">
-        <v>20250416093649</v>
-      </c>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1168,18 +1141,9 @@
       <c r="AL5" t="s">
         <v>56</v>
       </c>
-      <c r="AM5">
-        <v>20250416094724.699</v>
-      </c>
       <c r="AN5" t="s">
         <v>56</v>
       </c>
-      <c r="AO5">
-        <v>20250416094731.699</v>
-      </c>
-      <c r="AP5">
-        <v>20250416094731.699</v>
-      </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -1239,18 +1203,9 @@
       <c r="AL6" t="s">
         <v>56</v>
       </c>
-      <c r="AM6">
-        <v>20250416095358.602</v>
-      </c>
       <c r="AN6" t="s">
         <v>56</v>
       </c>
-      <c r="AO6">
-        <v>20250416095358.602</v>
-      </c>
-      <c r="AP6">
-        <v>20250416095358.602</v>
-      </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1313,18 +1268,9 @@
       <c r="AL7" t="s">
         <v>64</v>
       </c>
-      <c r="AM7">
-        <v>20250417130153.398</v>
-      </c>
       <c r="AN7" t="s">
         <v>64</v>
       </c>
-      <c r="AO7">
-        <v>20250417130153.398</v>
-      </c>
-      <c r="AP7">
-        <v>20250417130153.398</v>
-      </c>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1387,18 +1333,9 @@
       <c r="AL8" t="s">
         <v>56</v>
       </c>
-      <c r="AM8">
-        <v>20250418124806</v>
-      </c>
       <c r="AN8" t="s">
         <v>56</v>
       </c>
-      <c r="AO8">
-        <v>20250418124918.301</v>
-      </c>
-      <c r="AP8">
-        <v>20250418124918.301</v>
-      </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1461,18 +1398,9 @@
       <c r="AL9" t="s">
         <v>52</v>
       </c>
-      <c r="AM9">
-        <v>20250420155503.398</v>
-      </c>
       <c r="AN9" t="s">
         <v>52</v>
       </c>
-      <c r="AO9">
-        <v>20250420155916.801</v>
-      </c>
-      <c r="AP9">
-        <v>20250420155916.801</v>
-      </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1535,18 +1463,9 @@
       <c r="AL10" t="s">
         <v>52</v>
       </c>
-      <c r="AM10">
-        <v>20250420161022.199</v>
-      </c>
       <c r="AN10" t="s">
         <v>52</v>
       </c>
-      <c r="AO10">
-        <v>20250420161347.801</v>
-      </c>
-      <c r="AP10">
-        <v>20250420161347.801</v>
-      </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1609,18 +1528,9 @@
       <c r="AL11" t="s">
         <v>52</v>
       </c>
-      <c r="AM11">
-        <v>20250420161526.398</v>
-      </c>
       <c r="AN11" t="s">
         <v>52</v>
       </c>
-      <c r="AO11">
-        <v>20250420163200.301</v>
-      </c>
-      <c r="AP11">
-        <v>20250420163200.301</v>
-      </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1689,18 +1599,9 @@
       <c r="AL12" t="s">
         <v>56</v>
       </c>
-      <c r="AM12">
-        <v>20250421091649</v>
-      </c>
       <c r="AN12" t="s">
         <v>56</v>
       </c>
-      <c r="AO12">
-        <v>20250421093105.699</v>
-      </c>
-      <c r="AP12">
-        <v>20250421093105.699</v>
-      </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1769,18 +1670,9 @@
       <c r="AL13" t="s">
         <v>56</v>
       </c>
-      <c r="AM13">
-        <v>20250421090955.898</v>
-      </c>
       <c r="AN13" t="s">
         <v>56</v>
       </c>
-      <c r="AO13">
-        <v>20250421091028.5</v>
-      </c>
-      <c r="AP13">
-        <v>20250421091028.5</v>
-      </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1849,18 +1741,9 @@
       <c r="AL14" t="s">
         <v>56</v>
       </c>
-      <c r="AM14">
-        <v>20250421094028.301</v>
-      </c>
       <c r="AN14" t="s">
         <v>56</v>
       </c>
-      <c r="AO14">
-        <v>20250421094045.199</v>
-      </c>
-      <c r="AP14">
-        <v>20250421094157</v>
-      </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1935,18 +1818,9 @@
       <c r="AL15" t="s">
         <v>56</v>
       </c>
-      <c r="AM15">
-        <v>20250421100839.102</v>
-      </c>
       <c r="AN15" t="s">
         <v>56</v>
       </c>
-      <c r="AO15">
-        <v>20250421101007.102</v>
-      </c>
-      <c r="AP15">
-        <v>20250421101007.102</v>
-      </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2015,20 +1889,11 @@
       <c r="AL16" t="s">
         <v>48</v>
       </c>
-      <c r="AM16">
-        <v>20250422103337.801</v>
-      </c>
       <c r="AN16" t="s">
         <v>48</v>
       </c>
-      <c r="AO16">
-        <v>20250422103337.801</v>
-      </c>
-      <c r="AP16">
-        <v>20250422103337.801</v>
-      </c>
-    </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
@@ -2095,20 +1960,11 @@
       <c r="AL17" t="s">
         <v>48</v>
       </c>
-      <c r="AM17">
-        <v>20250422103945.898</v>
-      </c>
       <c r="AN17" t="s">
         <v>48</v>
       </c>
-      <c r="AO17">
-        <v>20250422103945.898</v>
-      </c>
-      <c r="AP17">
-        <v>20250422103945.898</v>
-      </c>
-    </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>43</v>
       </c>
@@ -2172,20 +2028,11 @@
       <c r="AL18" t="s">
         <v>48</v>
       </c>
-      <c r="AM18">
-        <v>20250422104204.602</v>
-      </c>
       <c r="AN18" t="s">
         <v>48</v>
       </c>
-      <c r="AO18">
-        <v>20250422104204.602</v>
-      </c>
-      <c r="AP18">
-        <v>20250422104204.602</v>
-      </c>
-    </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -2249,20 +2096,11 @@
       <c r="AL19" t="s">
         <v>48</v>
       </c>
-      <c r="AM19">
-        <v>20250422104303</v>
-      </c>
       <c r="AN19" t="s">
         <v>48</v>
       </c>
-      <c r="AO19">
-        <v>20250422104303</v>
-      </c>
-      <c r="AP19">
-        <v>20250422104303</v>
-      </c>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>43</v>
       </c>
@@ -2326,20 +2164,11 @@
       <c r="AL20" t="s">
         <v>48</v>
       </c>
-      <c r="AM20">
-        <v>20250422104343.699</v>
-      </c>
       <c r="AN20" t="s">
         <v>48</v>
       </c>
-      <c r="AO20">
-        <v>20250422104343.699</v>
-      </c>
-      <c r="AP20">
-        <v>20250422104343.699</v>
-      </c>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,20 +2232,11 @@
       <c r="AL21" t="s">
         <v>48</v>
       </c>
-      <c r="AM21">
-        <v>20250422105329.301</v>
-      </c>
       <c r="AN21" t="s">
         <v>48</v>
       </c>
-      <c r="AO21">
-        <v>20250422105329.301</v>
-      </c>
-      <c r="AP21">
-        <v>20250422105329.301</v>
-      </c>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -2480,20 +2300,11 @@
       <c r="AL22" t="s">
         <v>48</v>
       </c>
-      <c r="AM22">
-        <v>20250422105601.301</v>
-      </c>
       <c r="AN22" t="s">
         <v>48</v>
       </c>
-      <c r="AO22">
-        <v>20250422105601.301</v>
-      </c>
-      <c r="AP22">
-        <v>20250422105601.301</v>
-      </c>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -2557,20 +2368,11 @@
       <c r="AL23" t="s">
         <v>48</v>
       </c>
-      <c r="AM23">
-        <v>20250422105921.102</v>
-      </c>
       <c r="AN23" t="s">
         <v>48</v>
       </c>
-      <c r="AO23">
-        <v>20250422105921.102</v>
-      </c>
-      <c r="AP23">
-        <v>20250422105921.102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>43</v>
       </c>
@@ -2634,20 +2436,11 @@
       <c r="AL24" t="s">
         <v>48</v>
       </c>
-      <c r="AM24">
-        <v>20250422111041.102</v>
-      </c>
       <c r="AN24" t="s">
         <v>48</v>
       </c>
-      <c r="AO24">
-        <v>20250422111041.102</v>
-      </c>
-      <c r="AP24">
-        <v>20250422111041.102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>43</v>
       </c>
@@ -2714,20 +2507,11 @@
       <c r="AL25" t="s">
         <v>48</v>
       </c>
-      <c r="AM25">
-        <v>20250422112536.398</v>
-      </c>
       <c r="AN25" t="s">
         <v>48</v>
       </c>
-      <c r="AO25">
-        <v>20250422112536.398</v>
-      </c>
-      <c r="AP25">
-        <v>20250422112536.398</v>
-      </c>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>43</v>
       </c>
@@ -2794,20 +2578,11 @@
       <c r="AL26" t="s">
         <v>56</v>
       </c>
-      <c r="AM26">
-        <v>20250422143553.199</v>
-      </c>
       <c r="AN26" t="s">
         <v>56</v>
       </c>
-      <c r="AO26">
-        <v>20250422143614.699</v>
-      </c>
-      <c r="AP26">
-        <v>20250422143614.699</v>
-      </c>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>43</v>
       </c>
@@ -2865,20 +2640,11 @@
       <c r="AL27" t="s">
         <v>56</v>
       </c>
-      <c r="AM27">
-        <v>20250423094603.602</v>
-      </c>
       <c r="AN27" t="s">
         <v>56</v>
       </c>
-      <c r="AO27">
-        <v>20250423094603.602</v>
-      </c>
-      <c r="AP27">
-        <v>20250423094603.602</v>
-      </c>
-    </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>43</v>
       </c>
@@ -2945,20 +2711,11 @@
       <c r="AL28" t="s">
         <v>56</v>
       </c>
-      <c r="AM28">
-        <v>20250423100647.398</v>
-      </c>
       <c r="AN28" t="s">
         <v>56</v>
       </c>
-      <c r="AO28">
-        <v>20250423100753.602</v>
-      </c>
-      <c r="AP28">
-        <v>20250423100753.602</v>
-      </c>
-    </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>43</v>
       </c>
@@ -3025,20 +2782,11 @@
       <c r="AL29" t="s">
         <v>48</v>
       </c>
-      <c r="AM29">
-        <v>20250423104438.5</v>
-      </c>
       <c r="AN29" t="s">
         <v>48</v>
       </c>
-      <c r="AO29">
-        <v>20250423104438.5</v>
-      </c>
-      <c r="AP29">
-        <v>20250423104438.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,20 +2853,11 @@
       <c r="AL30" t="s">
         <v>48</v>
       </c>
-      <c r="AM30">
-        <v>20250423104649.5</v>
-      </c>
       <c r="AN30" t="s">
         <v>48</v>
       </c>
-      <c r="AO30">
-        <v>20250423104954.602</v>
-      </c>
-      <c r="AP30">
-        <v>20250423104954.602</v>
-      </c>
-    </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>43</v>
       </c>
@@ -3185,20 +2924,11 @@
       <c r="AL31" t="s">
         <v>48</v>
       </c>
-      <c r="AM31">
-        <v>20250423105024.301</v>
-      </c>
       <c r="AN31" t="s">
         <v>48</v>
       </c>
-      <c r="AO31">
-        <v>20250423105511.898</v>
-      </c>
-      <c r="AP31">
-        <v>20250423105511.898</v>
-      </c>
-    </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>43</v>
       </c>
@@ -3265,20 +2995,11 @@
       <c r="AL32" t="s">
         <v>48</v>
       </c>
-      <c r="AM32">
-        <v>20250423105645.102</v>
-      </c>
       <c r="AN32" t="s">
         <v>48</v>
       </c>
-      <c r="AO32">
-        <v>20250423110102.102</v>
-      </c>
-      <c r="AP32">
-        <v>20250423110102.102</v>
-      </c>
-    </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>43</v>
       </c>
@@ -3345,20 +3066,11 @@
       <c r="AL33" t="s">
         <v>56</v>
       </c>
-      <c r="AM33">
-        <v>20250423110750.199</v>
-      </c>
       <c r="AN33" t="s">
         <v>56</v>
       </c>
-      <c r="AO33">
-        <v>20250423110750.199</v>
-      </c>
-      <c r="AP33">
-        <v>20250423110750.199</v>
-      </c>
-    </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
@@ -3425,20 +3137,11 @@
       <c r="AL34" t="s">
         <v>48</v>
       </c>
-      <c r="AM34">
-        <v>20250423110429.5</v>
-      </c>
       <c r="AN34" t="s">
         <v>48</v>
       </c>
-      <c r="AO34">
-        <v>20250423110546</v>
-      </c>
-      <c r="AP34">
-        <v>20250423110546</v>
-      </c>
-    </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
@@ -3505,20 +3208,11 @@
       <c r="AL35" t="s">
         <v>48</v>
       </c>
-      <c r="AM35">
-        <v>20250423111008.898</v>
-      </c>
       <c r="AN35" t="s">
         <v>48</v>
       </c>
-      <c r="AO35">
-        <v>20250423111127.398</v>
-      </c>
-      <c r="AP35">
-        <v>20250423111127.398</v>
-      </c>
-    </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
@@ -3585,20 +3279,11 @@
       <c r="AL36" t="s">
         <v>48</v>
       </c>
-      <c r="AM36">
-        <v>20250423111343.301</v>
-      </c>
       <c r="AN36" t="s">
         <v>48</v>
       </c>
-      <c r="AO36">
-        <v>20250423111420.301</v>
-      </c>
-      <c r="AP36">
-        <v>20250423111420.301</v>
-      </c>
-    </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -3659,20 +3344,11 @@
       <c r="AL37" t="s">
         <v>52</v>
       </c>
-      <c r="AM37">
-        <v>20250423111835.199</v>
-      </c>
       <c r="AN37" t="s">
         <v>52</v>
       </c>
-      <c r="AO37">
-        <v>20250423111835.199</v>
-      </c>
-      <c r="AP37">
-        <v>20250423111835.199</v>
-      </c>
-    </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>43</v>
       </c>
@@ -3742,20 +3418,11 @@
       <c r="AL38" t="s">
         <v>56</v>
       </c>
-      <c r="AM38">
-        <v>20250423113508.898</v>
-      </c>
       <c r="AN38" t="s">
         <v>56</v>
       </c>
-      <c r="AO38">
-        <v>20250423113529.699</v>
-      </c>
-      <c r="AP38">
-        <v>20250423113529.699</v>
-      </c>
-    </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>43</v>
       </c>
@@ -3825,20 +3492,11 @@
       <c r="AL39" t="s">
         <v>56</v>
       </c>
-      <c r="AM39">
-        <v>20250423155552.602</v>
-      </c>
       <c r="AN39" t="s">
         <v>56</v>
       </c>
-      <c r="AO39">
-        <v>20250423155653.301</v>
-      </c>
-      <c r="AP39">
-        <v>20250423155653.301</v>
-      </c>
-    </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -3908,20 +3566,11 @@
       <c r="AL40" t="s">
         <v>56</v>
       </c>
-      <c r="AM40">
-        <v>20250423113913.602</v>
-      </c>
       <c r="AN40" t="s">
         <v>56</v>
       </c>
-      <c r="AO40">
-        <v>20250423113942.699</v>
-      </c>
-      <c r="AP40">
-        <v>20250423113942.699</v>
-      </c>
-    </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>43</v>
       </c>
@@ -3982,20 +3631,11 @@
       <c r="AL41" t="s">
         <v>64</v>
       </c>
-      <c r="AM41">
-        <v>20250424062346.801</v>
-      </c>
       <c r="AN41" t="s">
         <v>64</v>
       </c>
-      <c r="AO41">
-        <v>20250424062346.801</v>
-      </c>
-      <c r="AP41">
-        <v>20250424062346.801</v>
-      </c>
-    </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -4065,20 +3705,11 @@
       <c r="AL42" t="s">
         <v>64</v>
       </c>
-      <c r="AM42">
-        <v>20250424062437.801</v>
-      </c>
       <c r="AN42" t="s">
         <v>64</v>
       </c>
-      <c r="AO42">
-        <v>20250424062437.801</v>
-      </c>
-      <c r="AP42">
-        <v>20250424062437.801</v>
-      </c>
-    </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
@@ -4148,20 +3779,11 @@
       <c r="AL43" t="s">
         <v>64</v>
       </c>
-      <c r="AM43">
-        <v>20250424062909.699</v>
-      </c>
       <c r="AN43" t="s">
         <v>64</v>
       </c>
-      <c r="AO43">
-        <v>20250424062909.699</v>
-      </c>
-      <c r="AP43">
-        <v>20250424062909.699</v>
-      </c>
-    </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -4222,20 +3844,11 @@
       <c r="AL44" t="s">
         <v>64</v>
       </c>
-      <c r="AM44">
-        <v>20250424064541.102</v>
-      </c>
       <c r="AN44" t="s">
         <v>64</v>
       </c>
-      <c r="AO44">
-        <v>20250424064541.102</v>
-      </c>
-      <c r="AP44">
-        <v>20250424064541.102</v>
-      </c>
-    </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
@@ -4296,17 +3909,8 @@
       <c r="AL45" t="s">
         <v>64</v>
       </c>
-      <c r="AM45">
-        <v>20250424065710.398</v>
-      </c>
       <c r="AN45" t="s">
         <v>64</v>
-      </c>
-      <c r="AO45">
-        <v>20250424065710.398</v>
-      </c>
-      <c r="AP45">
-        <v>20250424065710.398</v>
       </c>
     </row>
   </sheetData>
